--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -302,7 +308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -391,72 +397,80 @@
       <c r="A11" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>14</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>28</v>
       </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s" s="2">
         <v>31</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -471,94 +485,94 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20250723120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,19 +63,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-07-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -308,7 +302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -397,80 +391,72 @@
       <c r="A11" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>14</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -485,94 +471,94 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>34</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="D6" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>53</v>
-      </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250723120000</t>
+    <t>20250919120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-23T12:00:00+01:00</t>
+    <t>2025-09-19T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,6 +72,12 @@
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -108,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1537</t>
+    <t>1550</t>
   </si>
   <si>
     <t>Code</t>
@@ -302,7 +308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -391,72 +397,80 @@
       <c r="A11" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>14</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>28</v>
       </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s" s="2">
         <v>31</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -471,94 +485,94 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250919120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1550</t>
+    <t>1555</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1555</t>
+    <t>1573</t>
   </si>
   <si>
     <t>Code</t>
@@ -129,6 +129,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -138,10 +141,16 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
@@ -501,78 +510,84 @@
       <c r="A2" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1573</t>
+    <t>1614</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1614</t>
+    <t>1630</t>
   </si>
   <si>
     <t>Code</t>
